--- a/Tasks of the team.xlsx
+++ b/Tasks of the team.xlsx
@@ -325,7 +325,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -363,10 +363,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -376,22 +376,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -436,7 +425,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -481,19 +470,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -501,44 +490,24 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -763,7 +732,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="10.51171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.85"/>
@@ -820,7 +789,7 @@
       <c r="F2" s="9" t="n">
         <v>46132</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="11" t="s">
         <v>12</v>
       </c>
     </row>
@@ -831,10 +800,10 @@
       <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -894,7 +863,7 @@
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -915,7 +884,7 @@
       <c r="B7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="14" t="s">
@@ -936,7 +905,7 @@
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="14" t="s">
@@ -957,10 +926,10 @@
       <c r="B9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -978,10 +947,10 @@
       <c r="B10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -999,10 +968,10 @@
       <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="7" t="s">
         <v>42</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -1020,10 +989,10 @@
       <c r="B12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="7" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -1041,10 +1010,10 @@
       <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="7" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -1062,10 +1031,10 @@
       <c r="B14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="7" t="s">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -1083,10 +1052,10 @@
       <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1104,8 +1073,8 @@
       <c r="B16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="8" t="s">
         <v>11</v>
       </c>
@@ -1121,10 +1090,10 @@
       <c r="B17" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E17" s="8" t="s">
@@ -1142,10 +1111,10 @@
       <c r="B18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="7" t="s">
         <v>63</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1163,10 +1132,10 @@
       <c r="B19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="7" t="s">
         <v>66</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -1178,45 +1147,25 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="18" t="n">
         <v>1552194582</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="0"/>
-      <c r="G20" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="0"/>
-      <c r="I20" s="0"/>
-      <c r="J20" s="0"/>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0"/>
-      <c r="N20" s="0"/>
-      <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
-      <c r="S20" s="0"/>
-      <c r="T20" s="0"/>
-      <c r="U20" s="0"/>
-      <c r="V20" s="0"/>
-      <c r="W20" s="0"/>
-      <c r="X20" s="0"/>
-      <c r="Y20" s="0"/>
-      <c r="Z20" s="0"/>
-      <c r="AA20" s="0"/>
+      <c r="E20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
@@ -1225,10 +1174,10 @@
       <c r="B21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="7" t="s">
         <v>71</v>
       </c>
       <c r="E21" s="8" t="s">
@@ -1246,10 +1195,10 @@
       <c r="B22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
       <c r="E22" s="8" t="s">
@@ -1267,10 +1216,10 @@
       <c r="B23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
       <c r="E23" s="8" t="s">
@@ -1288,10 +1237,10 @@
       <c r="B24" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="7" t="s">
         <v>81</v>
       </c>
       <c r="E24" s="8" t="s">
@@ -1309,10 +1258,10 @@
       <c r="B25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="7" t="s">
         <v>84</v>
       </c>
       <c r="E25" s="8" t="s">
@@ -1324,45 +1273,25 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="18" t="n">
         <v>1040739210</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="0"/>
-      <c r="G26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="0"/>
-      <c r="I26" s="0"/>
-      <c r="J26" s="0"/>
-      <c r="K26" s="0"/>
-      <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
-      <c r="N26" s="0"/>
-      <c r="O26" s="0"/>
-      <c r="P26" s="0"/>
-      <c r="Q26" s="0"/>
-      <c r="R26" s="0"/>
-      <c r="S26" s="0"/>
-      <c r="T26" s="0"/>
-      <c r="U26" s="0"/>
-      <c r="V26" s="0"/>
-      <c r="W26" s="0"/>
-      <c r="X26" s="0"/>
-      <c r="Y26" s="0"/>
-      <c r="Z26" s="0"/>
-      <c r="AA26" s="0"/>
+      <c r="E26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
@@ -1371,10 +1300,10 @@
       <c r="B27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="7" t="s">
         <v>90</v>
       </c>
       <c r="E27" s="8" t="s">
@@ -1386,70 +1315,26 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-      <c r="C28" s="22" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="0"/>
-      <c r="G28" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="0"/>
-      <c r="I28" s="0"/>
-      <c r="J28" s="0"/>
-      <c r="K28" s="0"/>
-      <c r="L28" s="0"/>
-      <c r="M28" s="0"/>
-      <c r="N28" s="0"/>
-      <c r="O28" s="0"/>
-      <c r="P28" s="0"/>
-      <c r="Q28" s="0"/>
-      <c r="R28" s="0"/>
-      <c r="S28" s="0"/>
-      <c r="T28" s="0"/>
-      <c r="U28" s="0"/>
-      <c r="V28" s="0"/>
-      <c r="W28" s="0"/>
-      <c r="X28" s="0"/>
-      <c r="Y28" s="0"/>
-      <c r="Z28" s="0"/>
-      <c r="AA28" s="0"/>
+      <c r="E28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="20" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-      <c r="C29" s="0"/>
-      <c r="D29" s="0"/>
-      <c r="E29" s="0"/>
-      <c r="F29" s="0"/>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
-      <c r="I29" s="0"/>
-      <c r="J29" s="0"/>
-      <c r="K29" s="0"/>
-      <c r="L29" s="0"/>
-      <c r="M29" s="0"/>
-      <c r="N29" s="0"/>
-      <c r="O29" s="0"/>
-      <c r="P29" s="0"/>
-      <c r="Q29" s="0"/>
-      <c r="R29" s="0"/>
-      <c r="S29" s="0"/>
-      <c r="T29" s="0"/>
-      <c r="U29" s="0"/>
-      <c r="V29" s="0"/>
-      <c r="W29" s="0"/>
-      <c r="X29" s="0"/>
-      <c r="Y29" s="0"/>
-      <c r="Z29" s="0"/>
-      <c r="AA29" s="0"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -1462,7 +1347,7 @@
         <v>11</v>
       </c>
       <c r="F30" s="9"/>
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1500,120 +1385,24 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0"/>
-      <c r="B33" s="0"/>
-      <c r="C33" s="0"/>
-      <c r="D33" s="0"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="0"/>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
-      <c r="I33" s="0"/>
-      <c r="J33" s="0"/>
-      <c r="K33" s="0"/>
-      <c r="L33" s="0"/>
-      <c r="M33" s="0"/>
-      <c r="N33" s="0"/>
-      <c r="O33" s="0"/>
-      <c r="P33" s="0"/>
-      <c r="Q33" s="0"/>
-      <c r="R33" s="0"/>
-      <c r="S33" s="0"/>
-      <c r="T33" s="0"/>
-      <c r="U33" s="0"/>
-      <c r="V33" s="0"/>
-      <c r="W33" s="0"/>
-      <c r="X33" s="0"/>
-      <c r="Y33" s="0"/>
-      <c r="Z33" s="0"/>
-      <c r="AA33" s="0"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="F33" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
-      <c r="B35" s="0"/>
-      <c r="C35" s="0"/>
-      <c r="D35" s="0"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="0"/>
-      <c r="G35" s="0"/>
-      <c r="H35" s="0"/>
-      <c r="I35" s="0"/>
-      <c r="J35" s="0"/>
-      <c r="K35" s="0"/>
-      <c r="L35" s="0"/>
-      <c r="M35" s="0"/>
-      <c r="N35" s="0"/>
-      <c r="O35" s="0"/>
-      <c r="P35" s="0"/>
-      <c r="Q35" s="0"/>
-      <c r="R35" s="0"/>
-      <c r="S35" s="0"/>
-      <c r="T35" s="0"/>
-      <c r="U35" s="0"/>
-      <c r="V35" s="0"/>
-      <c r="W35" s="0"/>
-      <c r="X35" s="0"/>
-      <c r="Y35" s="0"/>
-      <c r="Z35" s="0"/>
-      <c r="AA35" s="0"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0"/>
-      <c r="B36" s="0"/>
-      <c r="C36" s="0"/>
-      <c r="D36" s="0"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="0"/>
-      <c r="G36" s="0"/>
-      <c r="H36" s="0"/>
-      <c r="I36" s="0"/>
-      <c r="J36" s="0"/>
-      <c r="K36" s="0"/>
-      <c r="L36" s="0"/>
-      <c r="M36" s="0"/>
-      <c r="N36" s="0"/>
-      <c r="O36" s="0"/>
-      <c r="P36" s="0"/>
-      <c r="Q36" s="0"/>
-      <c r="R36" s="0"/>
-      <c r="S36" s="0"/>
-      <c r="T36" s="0"/>
-      <c r="U36" s="0"/>
-      <c r="V36" s="0"/>
-      <c r="W36" s="0"/>
-      <c r="X36" s="0"/>
-      <c r="Y36" s="0"/>
-      <c r="Z36" s="0"/>
-      <c r="AA36" s="0"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="F36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0"/>
-      <c r="B37" s="0"/>
-      <c r="C37" s="0"/>
-      <c r="D37" s="0"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="0"/>
-      <c r="G37" s="0"/>
-      <c r="H37" s="0"/>
-      <c r="I37" s="0"/>
-      <c r="J37" s="0"/>
-      <c r="K37" s="0"/>
-      <c r="L37" s="0"/>
-      <c r="M37" s="0"/>
-      <c r="N37" s="0"/>
-      <c r="O37" s="0"/>
-      <c r="P37" s="0"/>
-      <c r="Q37" s="0"/>
-      <c r="R37" s="0"/>
-      <c r="S37" s="0"/>
-      <c r="T37" s="0"/>
-      <c r="U37" s="0"/>
-      <c r="V37" s="0"/>
-      <c r="W37" s="0"/>
-      <c r="X37" s="0"/>
-      <c r="Y37" s="0"/>
-      <c r="Z37" s="0"/>
-      <c r="AA37" s="0"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="F37" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Tasks of the team.xlsx
+++ b/Tasks of the team.xlsx
@@ -320,10 +320,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="mm/dd/yy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -425,7 +426,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,14 +471,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -500,6 +501,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -540,8 +545,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H32"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Phone"/>
@@ -789,7 +794,7 @@
       <c r="F2" s="9" t="n">
         <v>46132</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -800,7 +805,7 @@
       <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="10" t="s">
@@ -809,7 +814,9 @@
       <c r="E3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="9"/>
+      <c r="F3" s="12" t="n">
+        <v>46132</v>
+      </c>
       <c r="G3" s="5" t="s">
         <v>12</v>
       </c>
@@ -830,7 +837,9 @@
       <c r="E4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="F4" s="12" t="n">
+        <v>46132</v>
+      </c>
       <c r="G4" s="5" t="s">
         <v>12</v>
       </c>
@@ -851,7 +860,9 @@
       <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="12" t="n">
+        <v>46132</v>
+      </c>
       <c r="G5" s="5" t="s">
         <v>12</v>
       </c>
@@ -872,7 +883,9 @@
       <c r="E6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="F6" s="12" t="n">
+        <v>46132</v>
+      </c>
       <c r="G6" s="5" t="s">
         <v>12</v>
       </c>
@@ -893,7 +906,9 @@
       <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="12" t="n">
+        <v>46132</v>
+      </c>
       <c r="G7" s="5" t="s">
         <v>12</v>
       </c>
@@ -914,7 +929,9 @@
       <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G8" s="5" t="s">
         <v>12</v>
       </c>
@@ -935,7 +952,9 @@
       <c r="E9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G9" s="5" t="s">
         <v>12</v>
       </c>
@@ -956,7 +975,9 @@
       <c r="E10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G10" s="5" t="s">
         <v>12</v>
       </c>
@@ -977,7 +998,9 @@
       <c r="E11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G11" s="5" t="s">
         <v>12</v>
       </c>
@@ -998,7 +1021,9 @@
       <c r="E12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="F12" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G12" s="5" t="s">
         <v>12</v>
       </c>
@@ -1019,7 +1044,9 @@
       <c r="E13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="9"/>
+      <c r="F13" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G13" s="5" t="s">
         <v>12</v>
       </c>
@@ -1040,7 +1067,9 @@
       <c r="E14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="9"/>
+      <c r="F14" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G14" s="5" t="s">
         <v>12</v>
       </c>
@@ -1061,7 +1090,9 @@
       <c r="E15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="9"/>
+      <c r="F15" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G15" s="5" t="s">
         <v>12</v>
       </c>
@@ -1078,7 +1109,9 @@
       <c r="E16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="9"/>
+      <c r="F16" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G16" s="5" t="s">
         <v>12</v>
       </c>
@@ -1099,7 +1132,9 @@
       <c r="E17" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="9"/>
+      <c r="F17" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G17" s="5" t="s">
         <v>12</v>
       </c>
@@ -1120,7 +1155,9 @@
       <c r="E18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="9"/>
+      <c r="F18" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G18" s="5" t="s">
         <v>12</v>
       </c>
@@ -1141,7 +1178,9 @@
       <c r="E19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G19" s="5" t="s">
         <v>12</v>
       </c>
@@ -1162,7 +1201,9 @@
       <c r="E20" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="19" t="n">
+        <v>46142</v>
+      </c>
       <c r="G20" s="5" t="s">
         <v>12</v>
       </c>
@@ -1183,7 +1224,9 @@
       <c r="E21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="9"/>
+      <c r="F21" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G21" s="5" t="s">
         <v>12</v>
       </c>
@@ -1204,7 +1247,9 @@
       <c r="E22" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="9"/>
+      <c r="F22" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G22" s="5" t="s">
         <v>12</v>
       </c>
@@ -1225,7 +1270,9 @@
       <c r="E23" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="9"/>
+      <c r="F23" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G23" s="5" t="s">
         <v>12</v>
       </c>
@@ -1246,7 +1293,9 @@
       <c r="E24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="9"/>
+      <c r="F24" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G24" s="5" t="s">
         <v>12</v>
       </c>
@@ -1267,7 +1316,9 @@
       <c r="E25" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="9"/>
+      <c r="F25" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G25" s="5" t="s">
         <v>12</v>
       </c>
@@ -1288,7 +1339,9 @@
       <c r="E26" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="1"/>
+      <c r="F26" s="19" t="n">
+        <v>46142</v>
+      </c>
       <c r="G26" s="5" t="s">
         <v>12</v>
       </c>
@@ -1309,14 +1362,16 @@
       <c r="E27" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="9"/>
+      <c r="F27" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G27" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1"/>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>86</v>
       </c>
       <c r="D28" s="7" t="s">
@@ -1325,8 +1380,10 @@
       <c r="E28" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="20" t="s">
+      <c r="F28" s="19" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G28" s="21" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1334,7 +1391,9 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="F29" s="19" t="n">
+        <v>46142</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -1346,7 +1405,9 @@
       <c r="E30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F30" s="9"/>
+      <c r="F30" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G30" s="5" t="s">
         <v>12</v>
       </c>
@@ -1362,7 +1423,9 @@
       <c r="E31" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="9"/>
+      <c r="F31" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G31" s="5" t="s">
         <v>12</v>
       </c>
@@ -1379,7 +1442,9 @@
       <c r="E32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F32" s="9"/>
+      <c r="F32" s="12" t="n">
+        <v>46142</v>
+      </c>
       <c r="G32" s="5" t="s">
         <v>12</v>
       </c>
